--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.90531533677273</v>
+        <v>4.047113742225569</v>
       </c>
       <c r="D2" t="n">
-        <v>25.74189270209106</v>
+        <v>4.183057564089798</v>
       </c>
       <c r="E2" t="n">
-        <v>13.06484725009176</v>
+        <v>2.123037678139911</v>
       </c>
       <c r="F2" t="n">
-        <v>9.395397847621458</v>
+        <v>1.526752150238487</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1.697583890917536</v>
+        <v>0.2758573822740997</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6944793700203757</v>
+        <v>0.1128528976283111</v>
       </c>
       <c r="E3" t="n">
-        <v>13.06484725009176</v>
+        <v>2.123037678139911</v>
       </c>
       <c r="F3" t="n">
-        <v>9.395397847621458</v>
+        <v>1.526752150238487</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.27882059609971</v>
+        <v>2.645308346866202</v>
       </c>
       <c r="D4" t="n">
-        <v>31.88667115622917</v>
+        <v>5.181584062887239</v>
       </c>
       <c r="E4" t="n">
-        <v>13.06484725009176</v>
+        <v>2.123037678139911</v>
       </c>
       <c r="F4" t="n">
-        <v>9.395397847621458</v>
+        <v>1.526752150238487</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.38523958879592</v>
+        <v>4.287601433179337</v>
       </c>
       <c r="D5" t="n">
-        <v>6.733139674819206</v>
+        <v>1.094135197158121</v>
       </c>
       <c r="E5" t="n">
-        <v>13.06484725009176</v>
+        <v>2.123037678139911</v>
       </c>
       <c r="F5" t="n">
-        <v>9.395397847621458</v>
+        <v>1.526752150238487</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.04438027328528</v>
+        <v>5.857211794408858</v>
       </c>
       <c r="D6" t="n">
-        <v>14.11645764408457</v>
+        <v>2.293924367163742</v>
       </c>
       <c r="E6" t="n">
-        <v>13.06484725009176</v>
+        <v>2.123037678139911</v>
       </c>
       <c r="F6" t="n">
-        <v>9.395397847621458</v>
+        <v>1.526752150238487</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.86154146165801</v>
+        <v>1.602500487519427</v>
       </c>
       <c r="D7" t="n">
-        <v>3.557855327974186</v>
+        <v>0.5781514907958052</v>
       </c>
       <c r="E7" t="n">
-        <v>13.06484725009176</v>
+        <v>2.123037678139911</v>
       </c>
       <c r="F7" t="n">
-        <v>9.395397847621458</v>
+        <v>1.526752150238487</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.77401501490141</v>
+        <v>5.650777439921479</v>
       </c>
       <c r="D8" t="n">
-        <v>4.040442745633462</v>
+        <v>0.6565719461654377</v>
       </c>
       <c r="E8" t="n">
-        <v>13.06484725009176</v>
+        <v>2.123037678139911</v>
       </c>
       <c r="F8" t="n">
-        <v>9.395397847621458</v>
+        <v>1.526752150238487</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.49614112069889</v>
+        <v>4.305622932113571</v>
       </c>
       <c r="D9" t="n">
-        <v>25.18556065606213</v>
+        <v>4.092653606610096</v>
       </c>
       <c r="E9" t="n">
-        <v>13.06484725009176</v>
+        <v>2.123037678139911</v>
       </c>
       <c r="F9" t="n">
-        <v>9.395397847621458</v>
+        <v>1.526752150238487</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.45964570929257</v>
+        <v>5.599692427760043</v>
       </c>
       <c r="D10" t="n">
-        <v>9.25261451390554</v>
+        <v>1.50354985850965</v>
       </c>
       <c r="E10" t="n">
-        <v>13.06484725009176</v>
+        <v>2.123037678139911</v>
       </c>
       <c r="F10" t="n">
-        <v>9.395397847621458</v>
+        <v>1.526752150238487</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.92726232205199</v>
+        <v>4.700680127333449</v>
       </c>
       <c r="D11" t="n">
-        <v>7.883163884411224</v>
+        <v>1.281014131216824</v>
       </c>
       <c r="E11" t="n">
-        <v>13.06484725009176</v>
+        <v>2.123037678139911</v>
       </c>
       <c r="F11" t="n">
-        <v>9.395397847621458</v>
+        <v>1.526752150238487</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.25566436547291</v>
+        <v>4.754045459389348</v>
       </c>
       <c r="D12" t="n">
-        <v>7.436247560280504</v>
+        <v>1.208390228545582</v>
       </c>
       <c r="E12" t="n">
-        <v>13.06484725009176</v>
+        <v>2.123037678139911</v>
       </c>
       <c r="F12" t="n">
-        <v>9.395397847621458</v>
+        <v>1.526752150238487</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>43.38826690905861</v>
+        <v>7.050593372722025</v>
       </c>
       <c r="D13" t="n">
-        <v>5.001005566530455</v>
+        <v>0.8126634045611989</v>
       </c>
       <c r="E13" t="n">
-        <v>13.06484725009176</v>
+        <v>2.123037678139911</v>
       </c>
       <c r="F13" t="n">
-        <v>9.395397847621458</v>
+        <v>1.526752150238487</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>53.59467970073734</v>
+        <v>8.70913545136982</v>
       </c>
       <c r="D14" t="n">
-        <v>12.79094161966155</v>
+        <v>2.078528013195002</v>
       </c>
       <c r="E14" t="n">
-        <v>13.06484725009176</v>
+        <v>2.123037678139911</v>
       </c>
       <c r="F14" t="n">
-        <v>9.395397847621458</v>
+        <v>1.526752150238487</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
